--- a/analysis/power_budget/Power Budget V1.xlsx
+++ b/analysis/power_budget/Power Budget V1.xlsx
@@ -4,8 +4,8 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Power Budget" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Passive Components" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Circuit Design" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="New Components" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Old Components" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="Motor Data Conversion" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="Battery" sheetId="5" r:id="rId9"/>
     <sheet state="visible" name="Power Notes" sheetId="6" r:id="rId10"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="452">
   <si>
     <t>Identification /  Role</t>
   </si>
@@ -769,211 +769,1283 @@
     <t>tells you how you’re using and placing it.</t>
   </si>
   <si>
+    <t>Domain: 16.8 V</t>
+  </si>
+  <si>
+    <t>Item #</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Ref Des</t>
+    </r>
+  </si>
+  <si>
+    <t>Qty per Board</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Qty</t>
+    </r>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Mfg Part #</t>
+    </r>
+  </si>
+  <si>
+    <t>Description / Value</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Package</t>
+    </r>
+  </si>
+  <si>
+    <t>Voltage - Rated</t>
+  </si>
+  <si>
+    <t>Current - Rated</t>
+  </si>
+  <si>
+    <t>Power - Rated</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Your Instructions / Notes</t>
+  </si>
+  <si>
+    <t>Unit Cost</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>Murata Electronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM21BR61H106KE43L
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Capacitor </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>10 uF</t>
+    </r>
+  </si>
+  <si>
+    <t>50 V</t>
+  </si>
+  <si>
+    <t>Surface Mount</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>U$55</t>
+  </si>
+  <si>
+    <t>Diodes Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP62300TWU-7 </t>
+  </si>
+  <si>
+    <t>5 V Buck Converter</t>
+  </si>
+  <si>
+    <t>SOT-23-6 Thin</t>
+  </si>
+  <si>
+    <t>18 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">link </t>
+  </si>
+  <si>
+    <t>Capacitor 1000 uF</t>
+  </si>
+  <si>
+    <t>35V</t>
+  </si>
+  <si>
+    <t>Capacitor 470 uF</t>
+  </si>
+  <si>
+    <t>Domain: 5V</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Ref Des</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Qty</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Mfg Part #</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Package</t>
+    </r>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>Samsung Electromechanics</t>
+  </si>
+  <si>
+    <t>CL05A104KA5NNNC</t>
+  </si>
+  <si>
+    <t>Capacitor 100nF</t>
+  </si>
+  <si>
+    <t>25V</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+LQM21PN3R3MGRD</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Inductor </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>3.3 µH</t>
+    </r>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>YAGEO</t>
+  </si>
+  <si>
+    <t>CC0402JRNPO9BN101</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Capacitor </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>100 pF</t>
+    </r>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>Panasonic Electronic Components</t>
+  </si>
+  <si>
+    <t>ERJ-2RKF5622X</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">Resistors </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>56.2k</t>
+    </r>
+  </si>
+  <si>
+    <t>0.1 W</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC1005F103CS </t>
+  </si>
+  <si>
+    <t>Resistors 10k</t>
+  </si>
+  <si>
+    <t>0.063 W</t>
+  </si>
+  <si>
+    <t>C2A,C2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+CL21A226MOQNNNE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Capacitor </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>22 µF</t>
+    </r>
+  </si>
+  <si>
+    <t>16V</t>
+  </si>
+  <si>
+    <t>Domain: 3.3V</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Ref Des</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Qty</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Mfg Part #</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Package</t>
+    </r>
+  </si>
+  <si>
+    <t>U33</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLV75533PDYDR </t>
+  </si>
+  <si>
+    <t>3.3 V LDO</t>
+  </si>
+  <si>
+    <t>SC-74A</t>
+  </si>
+  <si>
+    <t>5.5 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surface Mount </t>
+  </si>
+  <si>
+    <t>C35, C36</t>
+  </si>
+  <si>
+    <t>CL05A105KP5NNNC</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Capacitor </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>1uF</t>
+    </r>
+  </si>
+  <si>
+    <t>10V</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+MCC (Micro Commercial Components)</t>
+  </si>
+  <si>
+    <t>SM5817PL-TP</t>
+  </si>
+  <si>
+    <t>Schottky Diode</t>
+  </si>
+  <si>
+    <t>SOD-123</t>
+  </si>
+  <si>
+    <t>20V</t>
+  </si>
+  <si>
+    <t>Bulk Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>50nH</t>
+  </si>
+  <si>
+    <t>150 nH</t>
+  </si>
+  <si>
+    <t>300 nH</t>
+  </si>
+  <si>
+    <t>600 nH</t>
+  </si>
+  <si>
+    <t>900 nH</t>
+  </si>
+  <si>
+    <t>1200 nH</t>
+  </si>
+  <si>
+    <t>1500 nH</t>
+  </si>
+  <si>
+    <t>Rankings</t>
+  </si>
+  <si>
+    <t>B41866C5108M000</t>
+  </si>
+  <si>
+    <t>1000 µF</t>
+  </si>
+  <si>
+    <t>110m Ohm</t>
+  </si>
+  <si>
+    <t>0.11 Ohm</t>
+  </si>
+  <si>
+    <t>15.084 V</t>
+  </si>
+  <si>
+    <t>13.45 V</t>
+  </si>
+  <si>
+    <t>12.602 V</t>
+  </si>
+  <si>
+    <t>12.61 V</t>
+  </si>
+  <si>
+    <t>12.775 V</t>
+  </si>
+  <si>
+    <t>12.975 V</t>
+  </si>
+  <si>
+    <t>13.154 V</t>
+  </si>
+  <si>
+    <t>EKYC250ELL821MJ16S</t>
+  </si>
+  <si>
+    <t>820 µF</t>
+  </si>
+  <si>
+    <t>100m Ohm</t>
+  </si>
+  <si>
+    <t>0.1 Ohm</t>
+  </si>
+  <si>
+    <t>14.671 V</t>
+  </si>
+  <si>
+    <t>13.107 V</t>
+  </si>
+  <si>
+    <t>12.609 V</t>
+  </si>
+  <si>
+    <t>12.717 V</t>
+  </si>
+  <si>
+    <t>13.009 V</t>
+  </si>
+  <si>
+    <t>13.261 V</t>
+  </si>
+  <si>
+    <t>13.485 V</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>EGXF250ELL751MJ16S</t>
+    </r>
+  </si>
+  <si>
+    <t>750 µF</t>
+  </si>
+  <si>
+    <t>94m Ohm</t>
+  </si>
+  <si>
+    <t>0.094 Ohm</t>
+  </si>
+  <si>
+    <t>14.401 V</t>
+  </si>
+  <si>
+    <t>12.904 V</t>
+  </si>
+  <si>
+    <t>12.827 V</t>
+  </si>
+  <si>
+    <t>13.161 V</t>
+  </si>
+  <si>
+    <t>13.445 V</t>
+  </si>
+  <si>
+    <t>13.696 V</t>
+  </si>
+  <si>
+    <t>EGXF250ELL911MK15S</t>
+  </si>
+  <si>
+    <t>910 µF</t>
+  </si>
+  <si>
+    <t>82m Ohm</t>
+  </si>
+  <si>
+    <t>0.082 Ohm</t>
+  </si>
+  <si>
+    <t>13.767 V</t>
+  </si>
+  <si>
+    <t>12.608 V</t>
+  </si>
+  <si>
+    <t>12.799 V</t>
+  </si>
+  <si>
+    <t>13.146 V</t>
+  </si>
+  <si>
+    <t>13.443 V</t>
+  </si>
+  <si>
+    <t>13.703 V</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>B41858C5477M000</t>
+    </r>
+  </si>
+  <si>
+    <t>470 µF</t>
+  </si>
+  <si>
+    <t>118m Ohm</t>
+  </si>
+  <si>
+    <t>0.118 Ohm</t>
+  </si>
+  <si>
+    <t>15.455 V</t>
+  </si>
+  <si>
+    <t>13.893 V</t>
+  </si>
+  <si>
+    <t>12.986 V</t>
+  </si>
+  <si>
+    <t>12.990 V</t>
+  </si>
+  <si>
+    <t>13.323 V</t>
+  </si>
+  <si>
+    <t>13.611 V</t>
+  </si>
+  <si>
+    <t>13.863 V</t>
+  </si>
+  <si>
+    <t>16.8 V</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Ref Des</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Qty</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Mfg Part #</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Package</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">GRM21BC81D106KE51L </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Capacitor </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>10 uF</t>
+    </r>
+  </si>
+  <si>
+    <t>20 V</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Ref Des</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Qty</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Mfg Part #</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Package</t>
+    </r>
+  </si>
+  <si>
+    <t>Bourns Inc.</t>
+  </si>
+  <si>
+    <t>CWF1610-3R3K</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Inductor </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>3.3 µH</t>
+    </r>
+  </si>
+  <si>
+    <t>500 mA</t>
+  </si>
+  <si>
+    <t>Wurth Electronik</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Capacitor </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>100 pF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">Resistors </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>56.2k</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CL05A226MQ5N6J8 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Capacitor </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>22 µF</t>
+    </r>
+  </si>
+  <si>
+    <t>6.3V</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Ref Des</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Qty</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Mfg Part #</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Package</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">Capacitor </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>1uF</t>
+    </r>
+  </si>
+  <si>
+    <t>onsemi</t>
+  </si>
+  <si>
+    <t>Motor DataSheet (2-blade)</t>
+  </si>
+  <si>
+    <t>14.8 V 4S</t>
+  </si>
+  <si>
+    <t>Thrust</t>
+  </si>
+  <si>
+    <t>Weight (lbs):</t>
+  </si>
+  <si>
+    <t>Hover Weight (g)</t>
+  </si>
+  <si>
+    <t>Ascend Weight (g)</t>
+  </si>
+  <si>
+    <t>Hover per motor (x4) (g):</t>
+  </si>
+  <si>
+    <t>Ascend per motor (x4 - Double) (g):</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Interpolation between 300g and 500g  (P340) (W):</t>
+  </si>
+  <si>
+    <t>P340 Total (W)</t>
+  </si>
+  <si>
+    <t>Interpolation between 500g and 700g  (P680) (W):</t>
+  </si>
+  <si>
+    <t>P680 Total (w)</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Hover per motor Current (A)</t>
+  </si>
+  <si>
+    <t>Hover Total Current (A)</t>
+  </si>
+  <si>
+    <t>Ascend per motor Current (A)</t>
+  </si>
+  <si>
+    <t>Ascend Total Current (A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efficiency </t>
+  </si>
+  <si>
+    <t>Hover Efficiency (g/W)</t>
+  </si>
+  <si>
+    <t>Ascend Efficiency (g/W)</t>
+  </si>
+  <si>
+    <t>Subsystem / Rail</t>
+  </si>
+  <si>
+    <t>Detailed Info</t>
+  </si>
+  <si>
+    <t>Battery (CNHL G+Plus 4S 3000 mAh 70C)</t>
+  </si>
+  <si>
+    <t>Type: 4S LiPo (14.8 V nominal, 16.8 V full, ~13.2 V under load). Capacity: 3.0 Ah (~44 Wh). Discharge: 70 C = 210 A continuous (~250 A burst). Connectors: XT90 main to XT60 branches. Bus caps: 1000–2200 µF ≥ 35 V + 4.7–10 µF ceramics near XT90. ESC caps: 470–1000 µF ≥ 35 V each + 1 µF + 0.1 µF ceramics. Optional TVS 22–26 V standoff and fuse/polyfuse. Feeds ESCs and 5 V buck.</t>
+  </si>
+  <si>
+    <t>Input: 14.8 V battery. Output: 5 V @ 1 A target. Efficiency ≈ 90–95%. Output ripple ≤ 50 mVpp. Inductor ≈ 10–22 µH, output caps 2×47 µF ceramics, input cap 47–100 µF electrolytic.</t>
+  </si>
+  <si>
+    <t>3.3 V LDO Regulator</t>
+  </si>
+  <si>
+    <t>Input: 5 V from buck. Output: 3.3 V @ 0.5 A target. Dropout ≤ 0.5 V. PSRR ≥ 60 dB @ 500 kHz. Input cap 4.7 µF, output cap 10 µF. Feeds MCU, IMU, baro, oscillator.</t>
+  </si>
+  <si>
+    <t>ESC / Motors</t>
+  </si>
+  <si>
+    <t>4× 40 A ESCs. Input: 13.2–16.8 V. Output: 3-phase AC to motors. Per-ESC caps: 470–1000 µF ≥ 35 V. Total current ≈ 100 A cont / 160 A peak.</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Duty Cycle</t>
+  </si>
+  <si>
+    <t>the percentage of time a signal is ON during one complete cycle</t>
+  </si>
+  <si>
+    <t>Duty Cycle = (Ton / T) x 100%</t>
+  </si>
+  <si>
+    <t>Duty Cycle = (I_typ / I_peak) x 100%</t>
+  </si>
+  <si>
+    <t>Voltage (V):</t>
+  </si>
+  <si>
+    <t>the electrical potential difference between two points</t>
+  </si>
+  <si>
+    <t>how much "push" or "pressure" an electric charge feels that makes current flow</t>
+  </si>
+  <si>
+    <t>Water analogy: Water pressure</t>
+  </si>
+  <si>
+    <t>Electrical Meanin: Push that drives electrons through a circuit</t>
+  </si>
+  <si>
+    <t>Curent (A)</t>
+  </si>
+  <si>
+    <t>Water analogy: Flow rate (gallons/sec)</t>
+  </si>
+  <si>
+    <t>Electrical meaning: How many electrons move per second</t>
+  </si>
+  <si>
+    <t>Resistance</t>
+  </si>
+  <si>
+    <t>Water analogy: Hose Width</t>
+  </si>
+  <si>
+    <t>Electrical meaning: How hard it is for ecltrons to flow</t>
+  </si>
+  <si>
     <t>Capacitors</t>
-  </si>
-  <si>
-    <t>µF</t>
-  </si>
-  <si>
-    <t>C37, C34</t>
-  </si>
-  <si>
-    <t>C32</t>
-  </si>
-  <si>
-    <t>C2A, C2B</t>
-  </si>
-  <si>
-    <t>pF</t>
-  </si>
-  <si>
-    <t>C33</t>
-  </si>
-  <si>
-    <t>C35,C36</t>
-  </si>
-  <si>
-    <t>Resistors</t>
-  </si>
-  <si>
-    <t>kΩ</t>
-  </si>
-  <si>
-    <t>R14</t>
-  </si>
-  <si>
-    <t>R15</t>
-  </si>
-  <si>
-    <t>R9</t>
-  </si>
-  <si>
-    <t>R11</t>
-  </si>
-  <si>
-    <t>Ω</t>
-  </si>
-  <si>
-    <t>R12</t>
-  </si>
-  <si>
-    <t>Inductors</t>
-  </si>
-  <si>
-    <t>µH</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Circuit Design</t>
-  </si>
-  <si>
-    <t>Motor DataSheet (2-blade)</t>
-  </si>
-  <si>
-    <t>14.8 V 4S</t>
-  </si>
-  <si>
-    <t>Thrust</t>
-  </si>
-  <si>
-    <t>Weight (lbs):</t>
-  </si>
-  <si>
-    <t>Hover Weight (g)</t>
-  </si>
-  <si>
-    <t>Ascend Weight (g)</t>
-  </si>
-  <si>
-    <t>Hover per motor (x4) (g):</t>
-  </si>
-  <si>
-    <t>Ascend per motor (x4 - Double) (g):</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Interpolation between 300g and 500g  (P340) (W):</t>
-  </si>
-  <si>
-    <t>P340 Total (W)</t>
-  </si>
-  <si>
-    <t>Interpolation between 500g and 700g  (P680) (W):</t>
-  </si>
-  <si>
-    <t>P680 Total (w)</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Hover per motor Current (A)</t>
-  </si>
-  <si>
-    <t>Hover Total Current (A)</t>
-  </si>
-  <si>
-    <t>Ascend per motor Current (A)</t>
-  </si>
-  <si>
-    <t>Ascend Total Current (A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Efficiency </t>
-  </si>
-  <si>
-    <t>Hover Efficiency (g/W)</t>
-  </si>
-  <si>
-    <t>Ascend Efficiency (g/W)</t>
-  </si>
-  <si>
-    <t>Subsystem / Rail</t>
-  </si>
-  <si>
-    <t>Detailed Info</t>
-  </si>
-  <si>
-    <t>Battery (CNHL G+Plus 4S 3000 mAh 70C)</t>
-  </si>
-  <si>
-    <t>Type: 4S LiPo (14.8 V nominal, 16.8 V full, ~13.2 V under load). Capacity: 3.0 Ah (~44 Wh). Discharge: 70 C = 210 A continuous (~250 A burst). Connectors: XT90 main to XT60 branches. Bus caps: 1000–2200 µF ≥ 35 V + 4.7–10 µF ceramics near XT90. ESC caps: 470–1000 µF ≥ 35 V each + 1 µF + 0.1 µF ceramics. Optional TVS 22–26 V standoff and fuse/polyfuse. Feeds ESCs and 5 V buck.</t>
-  </si>
-  <si>
-    <t>5 V Buck Converter</t>
-  </si>
-  <si>
-    <t>Input: 14.8 V battery. Output: 5 V @ 1 A target. Efficiency ≈ 90–95%. Output ripple ≤ 50 mVpp. Inductor ≈ 10–22 µH, output caps 2×47 µF ceramics, input cap 47–100 µF electrolytic.</t>
-  </si>
-  <si>
-    <t>3.3 V LDO Regulator</t>
-  </si>
-  <si>
-    <t>Input: 5 V from buck. Output: 3.3 V @ 0.5 A target. Dropout ≤ 0.5 V. PSRR ≥ 60 dB @ 500 kHz. Input cap 4.7 µF, output cap 10 µF. Feeds MCU, IMU, baro, oscillator.</t>
-  </si>
-  <si>
-    <t>ESC / Motors</t>
-  </si>
-  <si>
-    <t>4× 40 A ESCs. Input: 13.2–16.8 V. Output: 3-phase AC to motors. Per-ESC caps: 470–1000 µF ≥ 35 V. Total current ≈ 100 A cont / 160 A peak.</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>Duty Cycle</t>
-  </si>
-  <si>
-    <t>the percentage of time a signal is ON during one complete cycle</t>
-  </si>
-  <si>
-    <t>Duty Cycle = (Ton / T) x 100%</t>
-  </si>
-  <si>
-    <t>Duty Cycle = (I_typ / I_peak) x 100%</t>
-  </si>
-  <si>
-    <t>Voltage (V):</t>
-  </si>
-  <si>
-    <t>the electrical potential difference between two points</t>
-  </si>
-  <si>
-    <t>how much "push" or "pressure" an electric charge feels that makes current flow</t>
-  </si>
-  <si>
-    <t>Water analogy: Water pressure</t>
-  </si>
-  <si>
-    <t>Electrical Meanin: Push that drives electrons through a circuit</t>
-  </si>
-  <si>
-    <t>Curent (A)</t>
-  </si>
-  <si>
-    <t>Water analogy: Flow rate (gallons/sec)</t>
-  </si>
-  <si>
-    <t>Electrical meaning: How many electrons move per second</t>
-  </si>
-  <si>
-    <t>Resistance</t>
-  </si>
-  <si>
-    <t>Water analogy: Hose Width</t>
-  </si>
-  <si>
-    <t>Electrical meaning: How hard it is for ecltrons to flow</t>
   </si>
   <si>
     <t>Capacitors are used in circuits for energy storage, smoothing voltage fluctuations</t>
@@ -1040,7 +2112,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="32">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1137,8 +2209,72 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF222222"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <color rgb="FF222222"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1187,8 +2323,14 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFBFBF"/>
+        <bgColor rgb="FFBFBFBF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border/>
     <border>
       <bottom style="thin">
@@ -1225,11 +2367,25 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="131">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1448,7 +2604,160 @@
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="5" fillId="9" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="14" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="14" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="5" fontId="13" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="13" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
@@ -9744,293 +11053,994 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="5" max="5" width="32.63"/>
+    <col customWidth="1" min="6" max="6" width="20.38"/>
+    <col customWidth="1" min="7" max="7" width="15.13"/>
+  </cols>
   <sheetData>
     <row r="2">
       <c r="A2" s="28" t="s">
         <v>207</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="74" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="75" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="D3" s="75" t="s">
+        <v>211</v>
+      </c>
+      <c r="E3" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="F3" s="75" t="s">
+        <v>213</v>
+      </c>
+      <c r="G3" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="H3" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="I3" s="78" t="s">
+        <v>216</v>
+      </c>
+      <c r="J3" s="78" t="s">
+        <v>217</v>
+      </c>
+      <c r="K3" s="78" t="s">
+        <v>218</v>
+      </c>
+      <c r="L3" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="M3" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="N3" s="74" t="s">
+        <v>221</v>
+      </c>
+      <c r="O3" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="P3" s="74" t="s">
+        <v>223</v>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="28">
+      <c r="A4" s="79">
+        <v>1.0</v>
+      </c>
+      <c r="B4" s="80" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="D4" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="83" t="s">
+        <v>225</v>
+      </c>
+      <c r="F4" s="84" t="s">
+        <v>226</v>
+      </c>
+      <c r="G4" s="85" t="s">
+        <v>227</v>
+      </c>
+      <c r="H4" s="86">
+        <v>805.0</v>
+      </c>
+      <c r="I4" s="87" t="s">
+        <v>228</v>
+      </c>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="M4" s="86"/>
+      <c r="N4" s="89">
+        <v>0.3</v>
+      </c>
+      <c r="O4" s="90">
+        <f t="shared" ref="O4:O5" si="1">D4*N4</f>
+        <v>0.3</v>
+      </c>
+      <c r="P4" s="91" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="79">
+        <v>2.0</v>
+      </c>
+      <c r="B5" s="80" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="D5" s="92">
+        <v>1.0</v>
+      </c>
+      <c r="E5" s="86" t="s">
+        <v>232</v>
+      </c>
+      <c r="F5" s="93" t="s">
+        <v>233</v>
+      </c>
+      <c r="G5" s="86" t="s">
+        <v>234</v>
+      </c>
+      <c r="H5" s="86" t="s">
+        <v>235</v>
+      </c>
+      <c r="I5" s="94" t="s">
+        <v>236</v>
+      </c>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="93" t="s">
+        <v>229</v>
+      </c>
+      <c r="M5" s="86"/>
+      <c r="N5" s="86">
+        <v>0.3</v>
+      </c>
+      <c r="O5" s="90">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="P5" s="95" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="96"/>
+      <c r="C6" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="98" t="s">
+        <v>238</v>
+      </c>
+      <c r="H6" s="97"/>
+      <c r="I6" s="99" t="s">
+        <v>239</v>
+      </c>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="98" t="s">
+        <v>229</v>
+      </c>
+      <c r="M6" s="97"/>
+      <c r="N6" s="97"/>
+      <c r="O6" s="97"/>
+      <c r="P6" s="97"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="98" t="s">
+        <v>240</v>
+      </c>
+      <c r="H7" s="97"/>
+      <c r="I7" s="98" t="s">
+        <v>239</v>
+      </c>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="98" t="s">
+        <v>229</v>
+      </c>
+      <c r="M7" s="97"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="97"/>
+      <c r="P7" s="97"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="74" t="s">
+        <v>208</v>
+      </c>
+      <c r="B12" s="75" t="s">
+        <v>242</v>
+      </c>
+      <c r="C12" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12" s="75" t="s">
+        <v>243</v>
+      </c>
+      <c r="E12" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" s="75" t="s">
+        <v>244</v>
+      </c>
+      <c r="G12" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="H12" s="77" t="s">
+        <v>245</v>
+      </c>
+      <c r="I12" s="78" t="s">
+        <v>216</v>
+      </c>
+      <c r="J12" s="78" t="s">
+        <v>217</v>
+      </c>
+      <c r="K12" s="78" t="s">
+        <v>218</v>
+      </c>
+      <c r="L12" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="M12" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="N12" s="74" t="s">
+        <v>221</v>
+      </c>
+      <c r="O12" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="P12" s="74" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="79">
+        <v>3.0</v>
+      </c>
+      <c r="B13" s="100" t="s">
+        <v>246</v>
+      </c>
+      <c r="C13" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="D13" s="96">
+        <v>1.0</v>
+      </c>
+      <c r="E13" s="101" t="s">
+        <v>247</v>
+      </c>
+      <c r="F13" s="102" t="s">
+        <v>248</v>
+      </c>
+      <c r="G13" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="H13" s="86">
+        <v>402.0</v>
+      </c>
+      <c r="I13" s="94" t="s">
+        <v>250</v>
+      </c>
+      <c r="J13" s="88"/>
+      <c r="K13" s="88"/>
+      <c r="L13" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="M13" s="86"/>
+      <c r="N13" s="89">
         <v>0.1</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="O13" s="90">
+        <f>C13*N13</f>
+        <v>0.1</v>
+      </c>
+      <c r="P13" s="95" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="79">
+        <v>4.0</v>
+      </c>
+      <c r="B14" s="80" t="s">
+        <v>251</v>
+      </c>
+      <c r="C14" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="E14" s="88" t="s">
+        <v>225</v>
+      </c>
+      <c r="F14" s="103" t="s">
+        <v>252</v>
+      </c>
+      <c r="G14" s="85" t="s">
+        <v>253</v>
+      </c>
+      <c r="H14" s="104">
+        <v>805.0</v>
+      </c>
+      <c r="I14" s="105"/>
+      <c r="J14" s="104" t="s">
+        <v>254</v>
+      </c>
+      <c r="K14" s="88"/>
+      <c r="L14" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="M14" s="86"/>
+      <c r="N14" s="89">
+        <v>0.17</v>
+      </c>
+      <c r="O14" s="90">
+        <f>D14*N14</f>
+        <v>0.17</v>
+      </c>
+      <c r="P14" s="106" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="79">
+        <v>5.0</v>
+      </c>
+      <c r="B15" s="80" t="s">
+        <v>255</v>
+      </c>
+      <c r="C15" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="E15" s="83" t="s">
+        <v>256</v>
+      </c>
+      <c r="F15" s="103" t="s">
+        <v>257</v>
+      </c>
+      <c r="G15" s="85" t="s">
+        <v>258</v>
+      </c>
+      <c r="H15" s="86">
+        <v>402.0</v>
+      </c>
+      <c r="I15" s="87" t="s">
+        <v>228</v>
+      </c>
+      <c r="J15" s="86"/>
+      <c r="K15" s="86"/>
+      <c r="L15" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="M15" s="86"/>
+      <c r="N15" s="107">
+        <v>0.08</v>
+      </c>
+      <c r="O15" s="90">
+        <f>C15*N15</f>
+        <v>0.08</v>
+      </c>
+      <c r="P15" s="106" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="79">
+        <v>6.0</v>
+      </c>
+      <c r="B16" s="80" t="s">
+        <v>259</v>
+      </c>
+      <c r="C16" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="D16" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="86" t="s">
+        <v>260</v>
+      </c>
+      <c r="F16" s="102" t="s">
+        <v>261</v>
+      </c>
+      <c r="G16" s="86" t="s">
+        <v>262</v>
+      </c>
+      <c r="H16" s="86">
+        <v>402.0</v>
+      </c>
+      <c r="I16" s="105"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="88" t="s">
+        <v>263</v>
+      </c>
+      <c r="L16" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="M16" s="86"/>
+      <c r="N16" s="90">
+        <v>0.1</v>
+      </c>
+      <c r="O16" s="90">
+        <f t="shared" ref="O16:O18" si="2">D16*N16</f>
+        <v>0.1</v>
+      </c>
+      <c r="P16" s="95" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="79">
+        <v>7.0</v>
+      </c>
+      <c r="B17" s="100" t="s">
+        <v>264</v>
+      </c>
+      <c r="C17" s="81">
+        <v>1.0</v>
+      </c>
+      <c r="D17" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="E17" s="101" t="s">
+        <v>247</v>
+      </c>
+      <c r="F17" s="102" t="s">
+        <v>265</v>
+      </c>
+      <c r="G17" s="86" t="s">
+        <v>266</v>
+      </c>
+      <c r="H17" s="86">
+        <v>402.0</v>
+      </c>
+      <c r="I17" s="105"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="88" t="s">
+        <v>267</v>
+      </c>
+      <c r="L17" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="M17" s="86"/>
+      <c r="N17" s="90">
+        <v>0.1</v>
+      </c>
+      <c r="O17" s="90">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="P17" s="95" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="79">
+        <v>8.0</v>
+      </c>
+      <c r="B18" s="80" t="s">
+        <v>268</v>
+      </c>
+      <c r="C18" s="81">
+        <v>2.0</v>
+      </c>
+      <c r="D18" s="92">
+        <v>2.0</v>
+      </c>
+      <c r="E18" s="101" t="s">
+        <v>247</v>
+      </c>
+      <c r="F18" s="103" t="s">
+        <v>269</v>
+      </c>
+      <c r="G18" s="85" t="s">
+        <v>270</v>
+      </c>
+      <c r="H18" s="104">
+        <v>805.0</v>
+      </c>
+      <c r="I18" s="87" t="s">
+        <v>271</v>
+      </c>
+      <c r="J18" s="86"/>
+      <c r="K18" s="86"/>
+      <c r="L18" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="M18" s="86"/>
+      <c r="N18" s="89">
+        <v>0.27</v>
+      </c>
+      <c r="O18" s="90">
+        <f t="shared" si="2"/>
+        <v>0.54</v>
+      </c>
+      <c r="P18" s="95" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="74" t="s">
         <v>208</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="D4" s="28">
+      <c r="B23" s="75" t="s">
+        <v>273</v>
+      </c>
+      <c r="C23" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="D23" s="75" t="s">
+        <v>274</v>
+      </c>
+      <c r="E23" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="F23" s="75" t="s">
+        <v>275</v>
+      </c>
+      <c r="G23" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="H23" s="77" t="s">
+        <v>276</v>
+      </c>
+      <c r="I23" s="78" t="s">
+        <v>216</v>
+      </c>
+      <c r="J23" s="78" t="s">
+        <v>217</v>
+      </c>
+      <c r="K23" s="78" t="s">
+        <v>218</v>
+      </c>
+      <c r="L23" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="M23" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="N23" s="74" t="s">
+        <v>221</v>
+      </c>
+      <c r="O23" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="P23" s="74" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="79">
+        <v>9.0</v>
+      </c>
+      <c r="B24" s="108" t="s">
+        <v>277</v>
+      </c>
+      <c r="C24" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="D24" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="E24" s="86" t="s">
+        <v>278</v>
+      </c>
+      <c r="F24" s="93" t="s">
+        <v>279</v>
+      </c>
+      <c r="G24" s="86" t="s">
+        <v>280</v>
+      </c>
+      <c r="H24" s="109" t="s">
+        <v>281</v>
+      </c>
+      <c r="I24" s="99" t="s">
+        <v>282</v>
+      </c>
+      <c r="J24" s="97"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="110" t="s">
+        <v>283</v>
+      </c>
+      <c r="M24" s="86"/>
+      <c r="N24" s="86">
+        <v>0.29</v>
+      </c>
+      <c r="O24" s="86">
+        <f>N24*D24</f>
+        <v>0.29</v>
+      </c>
+      <c r="P24" s="111" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="79">
+        <v>10.0</v>
+      </c>
+      <c r="B25" s="100" t="s">
+        <v>284</v>
+      </c>
+      <c r="C25" s="23">
         <v>2.0</v>
       </c>
-      <c r="F4" s="28">
-        <v>0.19</v>
-      </c>
-      <c r="G4" s="28">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="28">
-        <v>10.0</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="D5" s="28">
+      <c r="D25" s="82">
+        <v>2.0</v>
+      </c>
+      <c r="E25" s="101" t="s">
+        <v>247</v>
+      </c>
+      <c r="F25" s="93" t="s">
+        <v>285</v>
+      </c>
+      <c r="G25" s="112" t="s">
+        <v>286</v>
+      </c>
+      <c r="H25" s="105">
+        <v>402.0</v>
+      </c>
+      <c r="I25" s="94" t="s">
+        <v>287</v>
+      </c>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="M25" s="86"/>
+      <c r="N25" s="89">
+        <v>0.1</v>
+      </c>
+      <c r="O25" s="90">
+        <f t="shared" ref="O25:O26" si="3">D25*N25</f>
+        <v>0.2</v>
+      </c>
+      <c r="P25" s="95" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="113">
+        <v>13.0</v>
+      </c>
+      <c r="B26" s="80" t="s">
+        <v>288</v>
+      </c>
+      <c r="C26" s="23">
         <v>1.0</v>
       </c>
-      <c r="F5" s="28">
-        <v>0.08</v>
-      </c>
-      <c r="G5" s="28">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="28">
-        <v>22.0</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="D6" s="28">
+      <c r="D26" s="92">
+        <v>1.0</v>
+      </c>
+      <c r="E26" s="101" t="s">
+        <v>289</v>
+      </c>
+      <c r="F26" s="86" t="s">
+        <v>290</v>
+      </c>
+      <c r="G26" s="85" t="s">
+        <v>291</v>
+      </c>
+      <c r="H26" s="114" t="s">
+        <v>292</v>
+      </c>
+      <c r="I26" s="114" t="s">
+        <v>293</v>
+      </c>
+      <c r="J26" s="115" t="s">
+        <v>254</v>
+      </c>
+      <c r="K26" s="116"/>
+      <c r="L26" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="M26" s="85"/>
+      <c r="N26" s="117">
+        <v>0.15</v>
+      </c>
+      <c r="O26" s="117">
+        <f t="shared" si="3"/>
+        <v>0.15</v>
+      </c>
+      <c r="P26" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q26" s="80"/>
+      <c r="R26" s="80"/>
+      <c r="S26" s="80"/>
+      <c r="T26" s="80"/>
+      <c r="U26" s="80"/>
+      <c r="V26" s="80"/>
+      <c r="W26" s="80"/>
+      <c r="X26" s="80"/>
+      <c r="Y26" s="80"/>
+      <c r="Z26" s="80"/>
+      <c r="AA26" s="80"/>
+      <c r="AB26" s="80"/>
+      <c r="AC26" s="80"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="H31" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="I31" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="J31" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="K31" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="L31" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="M31" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="N31" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="O31" s="28" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D32" s="118" t="s">
+        <v>305</v>
+      </c>
+      <c r="E32" s="118" t="s">
+        <v>306</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="G32" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="H32" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="I32" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="J32" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="K32" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="L32" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="M32" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="N32" s="28" t="s">
+        <v>314</v>
+      </c>
+      <c r="O32" s="28">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="D33" s="118" t="s">
+        <v>316</v>
+      </c>
+      <c r="E33" s="118" t="s">
+        <v>317</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>318</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>319</v>
+      </c>
+      <c r="I33" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="J33" s="28" t="s">
+        <v>321</v>
+      </c>
+      <c r="K33" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="L33" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="M33" s="28" t="s">
+        <v>324</v>
+      </c>
+      <c r="N33" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="O33" s="28">
         <v>2.0</v>
       </c>
-      <c r="F6" s="28">
-        <v>0.17</v>
-      </c>
-      <c r="G6" s="28">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="28">
-        <v>100.0</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="D7" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="F7" s="28">
-        <v>0.05</v>
-      </c>
-      <c r="G7" s="28">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="D8" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="F8" s="28">
-        <v>0.15</v>
-      </c>
-      <c r="G8" s="28">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="E9" s="74">
-        <f>sum(D4:D8)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="28" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="28">
-        <v>47.0</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="D12" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="F12" s="28">
-        <v>0.14</v>
-      </c>
-      <c r="G12" s="28">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="28">
+    </row>
+    <row r="34">
+      <c r="B34" s="72" t="s">
+        <v>326</v>
+      </c>
+      <c r="D34" s="118" t="s">
+        <v>327</v>
+      </c>
+      <c r="E34" s="118" t="s">
+        <v>328</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="H34" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="J34" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="K34" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="L34" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="M34" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="N34" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="O34" s="28">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="D35" s="118" t="s">
+        <v>337</v>
+      </c>
+      <c r="E35" s="118" t="s">
+        <v>338</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="G35" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="H35" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="I35" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="J35" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="K35" s="28" t="s">
+        <v>342</v>
+      </c>
+      <c r="L35" s="28" t="s">
+        <v>343</v>
+      </c>
+      <c r="M35" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="N35" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="O35" s="28">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="72" t="s">
+        <v>346</v>
+      </c>
+      <c r="C36" s="119"/>
+      <c r="D36" s="118" t="s">
+        <v>347</v>
+      </c>
+      <c r="E36" s="118" t="s">
+        <v>348</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="G36" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="H36" s="28" t="s">
+        <v>350</v>
+      </c>
+      <c r="I36" s="28" t="s">
+        <v>351</v>
+      </c>
+      <c r="J36" s="28" t="s">
+        <v>352</v>
+      </c>
+      <c r="K36" s="28" t="s">
+        <v>353</v>
+      </c>
+      <c r="L36" s="28" t="s">
+        <v>354</v>
+      </c>
+      <c r="M36" s="28" t="s">
+        <v>355</v>
+      </c>
+      <c r="N36" s="28" t="s">
+        <v>356</v>
+      </c>
+      <c r="O36" s="28">
         <v>5.0</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="D13" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="F13" s="28">
-        <v>0.19</v>
-      </c>
-      <c r="G13" s="28">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="D14" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="F14" s="28">
-        <v>0.14</v>
-      </c>
-      <c r="G14" s="28">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="28">
-        <v>56.2</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="D15" s="28"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="28">
-        <v>56.0</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="F16" s="28">
-        <v>0.35</v>
-      </c>
-      <c r="G16" s="28">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="28">
-        <v>200.0</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="F17" s="28">
-        <v>0.14</v>
-      </c>
-      <c r="G17" s="28">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="28">
-        <v>10.0</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="D18" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="F18" s="28">
-        <v>0.14</v>
-      </c>
-      <c r="G18" s="28">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="E19" s="74">
-        <f>sum(D12:D18)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="28" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="28">
-        <v>3.3</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="D22" s="28">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="E23" s="74">
-        <f>sum(D22)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="D25" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="E25" s="74">
-        <f>sum(E9,E19,E23)</f>
-        <v>14</v>
-      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="P4"/>
+    <hyperlink r:id="rId2" ref="P5"/>
+    <hyperlink r:id="rId3" ref="P13"/>
+    <hyperlink r:id="rId4" ref="P14"/>
+    <hyperlink r:id="rId5" ref="P15"/>
+    <hyperlink r:id="rId6" ref="P16"/>
+    <hyperlink r:id="rId7" ref="P17"/>
+    <hyperlink r:id="rId8" ref="P18"/>
+    <hyperlink r:id="rId9" ref="P24"/>
+    <hyperlink r:id="rId10" ref="P25"/>
+    <hyperlink r:id="rId11" ref="P26"/>
+    <hyperlink r:id="rId12" ref="B32"/>
+    <hyperlink r:id="rId13" ref="B33"/>
+    <hyperlink r:id="rId14" ref="B34"/>
+    <hyperlink r:id="rId15" ref="B35"/>
+    <hyperlink r:id="rId16" ref="B36"/>
+  </hyperlinks>
+  <drawing r:id="rId17"/>
 </worksheet>
 </file>
 
@@ -10040,17 +12050,810 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="5.88"/>
+    <col customWidth="1" min="2" max="2" width="42.38"/>
+    <col customWidth="1" min="3" max="3" width="4.38"/>
+    <col customWidth="1" min="4" max="4" width="26.13"/>
+    <col customWidth="1" min="5" max="5" width="18.75"/>
+    <col customWidth="1" min="6" max="6" width="15.13"/>
+    <col customWidth="1" min="7" max="7" width="11.38"/>
+    <col customWidth="1" min="8" max="10" width="7.88"/>
+    <col customWidth="1" min="11" max="11" width="12.0"/>
+    <col customWidth="1" min="12" max="12" width="11.5"/>
+    <col customWidth="1" min="13" max="13" width="8.38"/>
+    <col customWidth="1" min="14" max="14" width="9.0"/>
+    <col customWidth="1" min="15" max="15" width="7.38"/>
+  </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="25" t="s">
-        <v>227</v>
-      </c>
+      <c r="A2" s="28" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="74" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="75" t="s">
+        <v>358</v>
+      </c>
+      <c r="C3" s="75" t="s">
+        <v>359</v>
+      </c>
+      <c r="D3" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="E3" s="75" t="s">
+        <v>360</v>
+      </c>
+      <c r="F3" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="G3" s="77" t="s">
+        <v>361</v>
+      </c>
+      <c r="H3" s="78" t="s">
+        <v>216</v>
+      </c>
+      <c r="I3" s="78" t="s">
+        <v>217</v>
+      </c>
+      <c r="J3" s="78" t="s">
+        <v>218</v>
+      </c>
+      <c r="K3" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="L3" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="M3" s="74" t="s">
+        <v>221</v>
+      </c>
+      <c r="N3" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="O3" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80"/>
+      <c r="AC3" s="80"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="113">
+        <v>9.0</v>
+      </c>
+      <c r="B4" s="80" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="92">
+        <v>1.0</v>
+      </c>
+      <c r="D4" s="101" t="s">
+        <v>247</v>
+      </c>
+      <c r="E4" s="93" t="s">
+        <v>362</v>
+      </c>
+      <c r="F4" s="112" t="s">
+        <v>363</v>
+      </c>
+      <c r="G4" s="86">
+        <v>805.0</v>
+      </c>
+      <c r="H4" s="94" t="s">
+        <v>364</v>
+      </c>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="L4" s="86"/>
+      <c r="M4" s="90">
+        <v>0.24</v>
+      </c>
+      <c r="N4" s="90">
+        <f t="shared" ref="N4:N5" si="1">C4*M4</f>
+        <v>0.24</v>
+      </c>
+      <c r="O4" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="100"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="80"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="80"/>
+      <c r="X4" s="80"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
+      <c r="AB4" s="80"/>
+      <c r="AC4" s="80"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="113">
+        <v>34.0</v>
+      </c>
+      <c r="B5" s="80" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="92">
+        <v>1.0</v>
+      </c>
+      <c r="D5" s="86" t="s">
+        <v>232</v>
+      </c>
+      <c r="E5" s="93" t="s">
+        <v>233</v>
+      </c>
+      <c r="F5" s="86" t="s">
+        <v>234</v>
+      </c>
+      <c r="G5" s="86" t="s">
+        <v>235</v>
+      </c>
+      <c r="H5" s="94" t="s">
+        <v>236</v>
+      </c>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="93" t="s">
+        <v>229</v>
+      </c>
+      <c r="L5" s="86"/>
+      <c r="M5" s="86">
+        <v>0.3</v>
+      </c>
+      <c r="N5" s="90">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="O5" s="111" t="s">
+        <v>237</v>
+      </c>
+      <c r="P5" s="80"/>
+      <c r="Q5" s="80"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="80"/>
+      <c r="T5" s="80"/>
+      <c r="U5" s="80"/>
+      <c r="V5" s="80"/>
+      <c r="W5" s="80"/>
+      <c r="X5" s="80"/>
+      <c r="Y5" s="80"/>
+      <c r="Z5" s="80"/>
+      <c r="AA5" s="80"/>
+      <c r="AB5" s="80"/>
+      <c r="AC5" s="80"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="74" t="s">
+        <v>208</v>
+      </c>
+      <c r="B10" s="75" t="s">
+        <v>365</v>
+      </c>
+      <c r="C10" s="75" t="s">
+        <v>366</v>
+      </c>
+      <c r="D10" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="E10" s="75" t="s">
+        <v>367</v>
+      </c>
+      <c r="F10" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="G10" s="77" t="s">
+        <v>368</v>
+      </c>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="L10" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="M10" s="74" t="s">
+        <v>221</v>
+      </c>
+      <c r="N10" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="O10" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="P10" s="80"/>
+      <c r="Q10" s="80"/>
+      <c r="R10" s="80"/>
+      <c r="S10" s="80"/>
+      <c r="T10" s="80"/>
+      <c r="U10" s="80"/>
+      <c r="V10" s="80"/>
+      <c r="W10" s="80"/>
+      <c r="X10" s="80"/>
+      <c r="Y10" s="80"/>
+      <c r="Z10" s="80"/>
+      <c r="AA10" s="80"/>
+      <c r="AB10" s="80"/>
+      <c r="AC10" s="80"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="113">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="100" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="D11" s="101" t="s">
+        <v>247</v>
+      </c>
+      <c r="E11" s="102" t="s">
+        <v>248</v>
+      </c>
+      <c r="F11" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="G11" s="86">
+        <v>402.0</v>
+      </c>
+      <c r="H11" s="94" t="s">
+        <v>250</v>
+      </c>
+      <c r="I11" s="88"/>
+      <c r="J11" s="88"/>
+      <c r="K11" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="L11" s="86"/>
+      <c r="M11" s="90">
+        <v>0.09</v>
+      </c>
+      <c r="N11" s="90">
+        <f t="shared" ref="N11:N16" si="2">C11*M11</f>
+        <v>0.09</v>
+      </c>
+      <c r="O11" s="120" t="s">
+        <v>230</v>
+      </c>
+      <c r="P11" s="80"/>
+      <c r="Q11" s="100"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="80"/>
+      <c r="U11" s="80"/>
+      <c r="V11" s="80"/>
+      <c r="W11" s="80"/>
+      <c r="X11" s="80"/>
+      <c r="Y11" s="80"/>
+      <c r="Z11" s="80"/>
+      <c r="AA11" s="80"/>
+      <c r="AB11" s="80"/>
+      <c r="AC11" s="80"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="113">
+        <v>21.0</v>
+      </c>
+      <c r="B12" s="80" t="s">
+        <v>251</v>
+      </c>
+      <c r="C12" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>369</v>
+      </c>
+      <c r="E12" s="102" t="s">
+        <v>370</v>
+      </c>
+      <c r="F12" s="85" t="s">
+        <v>371</v>
+      </c>
+      <c r="G12" s="86">
+        <v>603.0</v>
+      </c>
+      <c r="H12" s="105"/>
+      <c r="I12" s="88" t="s">
+        <v>372</v>
+      </c>
+      <c r="J12" s="88"/>
+      <c r="K12" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="L12" s="86"/>
+      <c r="M12" s="90">
+        <v>0.15</v>
+      </c>
+      <c r="N12" s="90">
+        <f t="shared" si="2"/>
+        <v>0.15</v>
+      </c>
+      <c r="O12" s="121" t="s">
+        <v>230</v>
+      </c>
+      <c r="P12" s="80"/>
+      <c r="Q12" s="80"/>
+      <c r="R12" s="80"/>
+      <c r="S12" s="80"/>
+      <c r="T12" s="80"/>
+      <c r="U12" s="80"/>
+      <c r="V12" s="80"/>
+      <c r="W12" s="80"/>
+      <c r="X12" s="80"/>
+      <c r="Y12" s="80"/>
+      <c r="Z12" s="80"/>
+      <c r="AA12" s="80"/>
+      <c r="AB12" s="80"/>
+      <c r="AC12" s="80"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="113">
+        <v>10.0</v>
+      </c>
+      <c r="B13" s="80" t="s">
+        <v>255</v>
+      </c>
+      <c r="C13" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="D13" s="101" t="s">
+        <v>373</v>
+      </c>
+      <c r="E13" s="102">
+        <v>8.85012005013E11</v>
+      </c>
+      <c r="F13" s="85" t="s">
+        <v>374</v>
+      </c>
+      <c r="G13" s="86">
+        <v>402.0</v>
+      </c>
+      <c r="H13" s="94" t="s">
+        <v>287</v>
+      </c>
+      <c r="I13" s="86"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="L13" s="86"/>
+      <c r="M13" s="122">
+        <v>0.1</v>
+      </c>
+      <c r="N13" s="90">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="O13" s="123" t="s">
+        <v>230</v>
+      </c>
+      <c r="P13" s="80"/>
+      <c r="Q13" s="80"/>
+      <c r="R13" s="80"/>
+      <c r="S13" s="80"/>
+      <c r="T13" s="80"/>
+      <c r="U13" s="80"/>
+      <c r="V13" s="80"/>
+      <c r="W13" s="80"/>
+      <c r="X13" s="80"/>
+      <c r="Y13" s="80"/>
+      <c r="Z13" s="80"/>
+      <c r="AA13" s="80"/>
+      <c r="AB13" s="80"/>
+      <c r="AC13" s="80"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="113">
+        <v>26.0</v>
+      </c>
+      <c r="B14" s="80" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="86" t="s">
+        <v>260</v>
+      </c>
+      <c r="E14" s="102" t="s">
+        <v>261</v>
+      </c>
+      <c r="F14" s="86" t="s">
+        <v>375</v>
+      </c>
+      <c r="G14" s="86">
+        <v>402.0</v>
+      </c>
+      <c r="H14" s="105"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="88" t="s">
+        <v>263</v>
+      </c>
+      <c r="K14" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="L14" s="86"/>
+      <c r="M14" s="90">
+        <v>0.1</v>
+      </c>
+      <c r="N14" s="90">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="O14" s="95" t="s">
+        <v>230</v>
+      </c>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="80"/>
+      <c r="R14" s="80"/>
+      <c r="S14" s="80"/>
+      <c r="T14" s="80"/>
+      <c r="U14" s="80"/>
+      <c r="V14" s="80"/>
+      <c r="W14" s="80"/>
+      <c r="X14" s="80"/>
+      <c r="Y14" s="80"/>
+      <c r="Z14" s="80"/>
+      <c r="AA14" s="80"/>
+      <c r="AB14" s="80"/>
+      <c r="AC14" s="80"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="113">
+        <v>22.0</v>
+      </c>
+      <c r="B15" s="100" t="s">
+        <v>264</v>
+      </c>
+      <c r="C15" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="101" t="s">
+        <v>247</v>
+      </c>
+      <c r="E15" s="102" t="s">
+        <v>265</v>
+      </c>
+      <c r="F15" s="86" t="s">
+        <v>266</v>
+      </c>
+      <c r="G15" s="86">
+        <v>402.0</v>
+      </c>
+      <c r="H15" s="105"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="88" t="s">
+        <v>267</v>
+      </c>
+      <c r="K15" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="L15" s="86"/>
+      <c r="M15" s="90">
+        <v>0.1</v>
+      </c>
+      <c r="N15" s="90">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="O15" s="95" t="s">
+        <v>230</v>
+      </c>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
+      <c r="S15" s="80"/>
+      <c r="T15" s="80"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="80"/>
+      <c r="X15" s="80"/>
+      <c r="Y15" s="80"/>
+      <c r="Z15" s="80"/>
+      <c r="AA15" s="80"/>
+      <c r="AB15" s="80"/>
+      <c r="AC15" s="80"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="113">
+        <v>4.0</v>
+      </c>
+      <c r="B16" s="80" t="s">
+        <v>268</v>
+      </c>
+      <c r="C16" s="92">
+        <v>2.0</v>
+      </c>
+      <c r="D16" s="101" t="s">
+        <v>247</v>
+      </c>
+      <c r="E16" s="102" t="s">
+        <v>376</v>
+      </c>
+      <c r="F16" s="85" t="s">
+        <v>377</v>
+      </c>
+      <c r="G16" s="86">
+        <v>402.0</v>
+      </c>
+      <c r="H16" s="94" t="s">
+        <v>378</v>
+      </c>
+      <c r="I16" s="86"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="L16" s="86"/>
+      <c r="M16" s="90">
+        <v>0.13</v>
+      </c>
+      <c r="N16" s="90">
+        <f t="shared" si="2"/>
+        <v>0.26</v>
+      </c>
+      <c r="O16" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="P16" s="80"/>
+      <c r="Q16" s="80"/>
+      <c r="R16" s="80"/>
+      <c r="S16" s="80"/>
+      <c r="T16" s="80"/>
+      <c r="U16" s="80"/>
+      <c r="V16" s="80"/>
+      <c r="W16" s="80"/>
+      <c r="X16" s="80"/>
+      <c r="Y16" s="80"/>
+      <c r="Z16" s="80"/>
+      <c r="AA16" s="80"/>
+      <c r="AB16" s="80"/>
+      <c r="AC16" s="80"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="74" t="s">
+        <v>208</v>
+      </c>
+      <c r="B20" s="75" t="s">
+        <v>379</v>
+      </c>
+      <c r="C20" s="75" t="s">
+        <v>380</v>
+      </c>
+      <c r="D20" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="E20" s="75" t="s">
+        <v>381</v>
+      </c>
+      <c r="F20" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="G20" s="77" t="s">
+        <v>382</v>
+      </c>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="L20" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="M20" s="74" t="s">
+        <v>221</v>
+      </c>
+      <c r="N20" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="O20" s="74" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="113">
+        <v>37.0</v>
+      </c>
+      <c r="B21" s="108" t="s">
+        <v>277</v>
+      </c>
+      <c r="C21" s="82">
+        <v>1.0</v>
+      </c>
+      <c r="D21" s="86" t="s">
+        <v>278</v>
+      </c>
+      <c r="E21" s="93" t="s">
+        <v>279</v>
+      </c>
+      <c r="F21" s="86" t="s">
+        <v>280</v>
+      </c>
+      <c r="G21" s="109" t="s">
+        <v>281</v>
+      </c>
+      <c r="H21" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="I21" s="97"/>
+      <c r="J21" s="97"/>
+      <c r="K21" s="110" t="s">
+        <v>283</v>
+      </c>
+      <c r="L21" s="86"/>
+      <c r="M21" s="86">
+        <v>0.29</v>
+      </c>
+      <c r="N21" s="86">
+        <f>M21*C21</f>
+        <v>0.29</v>
+      </c>
+      <c r="O21" s="111" t="s">
+        <v>237</v>
+      </c>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="80"/>
+      <c r="R21" s="80"/>
+      <c r="S21" s="80"/>
+      <c r="T21" s="80"/>
+      <c r="U21" s="80"/>
+      <c r="V21" s="80"/>
+      <c r="W21" s="80"/>
+      <c r="X21" s="80"/>
+      <c r="Y21" s="80"/>
+      <c r="Z21" s="80"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="113">
+        <v>7.0</v>
+      </c>
+      <c r="B22" s="100" t="s">
+        <v>284</v>
+      </c>
+      <c r="C22" s="82">
+        <v>2.0</v>
+      </c>
+      <c r="D22" s="101" t="s">
+        <v>247</v>
+      </c>
+      <c r="E22" s="93" t="s">
+        <v>285</v>
+      </c>
+      <c r="F22" s="112" t="s">
+        <v>383</v>
+      </c>
+      <c r="G22" s="105">
+        <v>402.0</v>
+      </c>
+      <c r="H22" s="94" t="s">
+        <v>287</v>
+      </c>
+      <c r="I22" s="86"/>
+      <c r="J22" s="86"/>
+      <c r="K22" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="L22" s="86"/>
+      <c r="M22" s="90">
+        <v>0.08</v>
+      </c>
+      <c r="N22" s="90">
+        <f t="shared" ref="N22:N23" si="3">C22*M22</f>
+        <v>0.16</v>
+      </c>
+      <c r="O22" s="95" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="113">
+        <v>13.0</v>
+      </c>
+      <c r="B23" s="80" t="s">
+        <v>288</v>
+      </c>
+      <c r="C23" s="92">
+        <v>1.0</v>
+      </c>
+      <c r="D23" s="101" t="s">
+        <v>384</v>
+      </c>
+      <c r="E23" s="88" t="s">
+        <v>290</v>
+      </c>
+      <c r="F23" s="85" t="s">
+        <v>291</v>
+      </c>
+      <c r="G23" s="114" t="s">
+        <v>292</v>
+      </c>
+      <c r="H23" s="124" t="s">
+        <v>293</v>
+      </c>
+      <c r="I23" s="88" t="s">
+        <v>372</v>
+      </c>
+      <c r="J23" s="125"/>
+      <c r="K23" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="L23" s="86"/>
+      <c r="M23" s="89">
+        <v>0.15</v>
+      </c>
+      <c r="N23" s="90">
+        <f t="shared" si="3"/>
+        <v>0.15</v>
+      </c>
+      <c r="O23" s="95" t="s">
+        <v>230</v>
+      </c>
+      <c r="P23" s="80"/>
+      <c r="Q23" s="80"/>
+      <c r="R23" s="80"/>
+      <c r="S23" s="80"/>
+      <c r="T23" s="80"/>
+      <c r="U23" s="80"/>
+      <c r="V23" s="80"/>
+      <c r="W23" s="80"/>
+      <c r="X23" s="80"/>
+      <c r="Y23" s="80"/>
+      <c r="Z23" s="80"/>
+      <c r="AA23" s="80"/>
+      <c r="AB23" s="80"/>
+      <c r="AC23" s="80"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="A2"/>
+    <hyperlink r:id="rId1" ref="O4"/>
+    <hyperlink r:id="rId2" ref="O5"/>
+    <hyperlink r:id="rId3" ref="O11"/>
+    <hyperlink r:id="rId4" ref="O12"/>
+    <hyperlink r:id="rId5" ref="O13"/>
+    <hyperlink r:id="rId6" ref="O14"/>
+    <hyperlink r:id="rId7" ref="O15"/>
+    <hyperlink r:id="rId8" ref="O16"/>
+    <hyperlink r:id="rId9" ref="O21"/>
+    <hyperlink r:id="rId10" ref="O22"/>
+    <hyperlink r:id="rId11" ref="O23"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId12"/>
 </worksheet>
 </file>
 
@@ -10066,12 +12869,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="s">
-        <v>228</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="42" t="s">
-        <v>229</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3">
@@ -10079,92 +12882,92 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="B4" s="75"/>
+        <v>387</v>
+      </c>
+      <c r="B4" s="126"/>
     </row>
     <row r="5">
       <c r="A5" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="B5" s="76">
+        <v>388</v>
+      </c>
+      <c r="B5" s="127">
         <v>3.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="B6" s="77">
+        <v>389</v>
+      </c>
+      <c r="B6" s="128">
         <f>sum(B5*453.59237)</f>
         <v>1360.77711</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="B7" s="77">
+        <v>390</v>
+      </c>
+      <c r="B7" s="128">
         <f>sum(B6*2)</f>
         <v>2721.55422</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="B8" s="77">
+        <v>391</v>
+      </c>
+      <c r="B8" s="128">
         <f>sum((B5*453.59237)/4)</f>
         <v>340.1942775</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="B9" s="77">
+        <v>392</v>
+      </c>
+      <c r="B9" s="128">
         <f>sum(((B5*453.59237)/4)*2)</f>
         <v>680.388555</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="78" t="s">
-        <v>236</v>
-      </c>
-      <c r="B11" s="75"/>
+      <c r="A11" s="129" t="s">
+        <v>393</v>
+      </c>
+      <c r="B11" s="126"/>
     </row>
     <row r="12">
       <c r="A12" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="B12" s="77">
+        <v>394</v>
+      </c>
+      <c r="B12" s="128">
         <f>sum(55.44+((340-300)/(500-300))*(100.8-55.44))</f>
         <v>64.512</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="B13" s="77">
+        <v>395</v>
+      </c>
+      <c r="B13" s="128">
         <f>sum(B12*4)</f>
         <v>258.048</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="B14" s="77">
+        <v>396</v>
+      </c>
+      <c r="B14" s="128">
         <f>sum(100.8+((680-500)/(700-500))*(136.08-100.8))</f>
         <v>132.552</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="B15" s="77">
+        <v>397</v>
+      </c>
+      <c r="B15" s="128">
         <f>sum(B14*4)</f>
         <v>530.208</v>
       </c>
@@ -10174,66 +12977,66 @@
     </row>
     <row r="17">
       <c r="A17" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="B17" s="75"/>
+        <v>398</v>
+      </c>
+      <c r="B17" s="126"/>
     </row>
     <row r="18">
       <c r="A18" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="B18" s="77">
+        <v>399</v>
+      </c>
+      <c r="B18" s="128">
         <f>sum(B12/14.8)</f>
         <v>4.358918919</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="B19" s="77">
+        <v>400</v>
+      </c>
+      <c r="B19" s="128">
         <f>sum(B18*4)</f>
         <v>17.43567568</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="B20" s="77">
+        <v>401</v>
+      </c>
+      <c r="B20" s="128">
         <f>sum(B14/14.8)</f>
         <v>8.956216216</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="28" t="s">
-        <v>245</v>
-      </c>
-      <c r="B21" s="77">
+        <v>402</v>
+      </c>
+      <c r="B21" s="128">
         <f>sum(B20*4)</f>
         <v>35.82486486</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="B23" s="75"/>
+        <v>403</v>
+      </c>
+      <c r="B23" s="126"/>
     </row>
     <row r="24">
       <c r="A24" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="B24" s="77">
+        <v>404</v>
+      </c>
+      <c r="B24" s="128">
         <f>sum(B8/B12)</f>
         <v>5.273348796</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="28" t="s">
-        <v>248</v>
-      </c>
-      <c r="B25" s="77">
+        <v>405</v>
+      </c>
+      <c r="B25" s="128">
         <f>sum(B9/B14)</f>
         <v>5.132993504</v>
       </c>
@@ -10270,42 +13073,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="s">
-        <v>249</v>
+        <v>406</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>250</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="79" t="s">
-        <v>251</v>
+      <c r="A2" s="130" t="s">
+        <v>408</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>252</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="28" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>254</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="28" t="s">
-        <v>255</v>
+        <v>411</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>256</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="28" t="s">
-        <v>257</v>
+        <v>413</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>258</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -10325,190 +13128,190 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="28" t="s">
-        <v>259</v>
+        <v>415</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>260</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="28" t="s">
-        <v>261</v>
+        <v>417</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>262</v>
+        <v>418</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="28" t="s">
-        <v>263</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="28" t="s">
-        <v>264</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="28" t="s">
-        <v>265</v>
+        <v>421</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>266</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="28" t="s">
-        <v>267</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="28" t="s">
-        <v>268</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="28" t="s">
-        <v>269</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="28" t="s">
-        <v>270</v>
+        <v>426</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>271</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="28" t="s">
-        <v>272</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="28" t="s">
-        <v>273</v>
+        <v>429</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>274</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="28" t="s">
-        <v>275</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="28" t="s">
-        <v>207</v>
+        <v>432</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>276</v>
+        <v>433</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="28" t="s">
-        <v>277</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="28" t="s">
-        <v>278</v>
+        <v>435</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="28" t="s">
-        <v>279</v>
+        <v>436</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="28" t="s">
-        <v>280</v>
+        <v>437</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="28" t="s">
-        <v>281</v>
+        <v>438</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="28" t="s">
-        <v>282</v>
+        <v>439</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="28" t="s">
-        <v>283</v>
+        <v>440</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="28" t="s">
-        <v>284</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="28" t="s">
-        <v>285</v>
+        <v>442</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="28" t="s">
-        <v>286</v>
+        <v>443</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="28" t="s">
-        <v>287</v>
+        <v>444</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="28" t="s">
-        <v>278</v>
+        <v>435</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="28" t="s">
-        <v>288</v>
+        <v>445</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="28" t="s">
-        <v>289</v>
+        <v>446</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="28" t="s">
-        <v>281</v>
+        <v>438</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="28" t="s">
-        <v>290</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="28" t="s">
-        <v>291</v>
+        <v>448</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="28" t="s">
-        <v>284</v>
+        <v>441</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="28" t="s">
-        <v>292</v>
+        <v>449</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="28" t="s">
-        <v>293</v>
+        <v>450</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="28" t="s">
-        <v>294</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
